--- a/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-8.xlsx
+++ b/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Desktop\App_Uv\AppAcompanhamientoUV\Doc_Test\Pruebas_Calidad\Pruebas_Unitarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869F83C0-9A22-4EEB-9F8B-6B1F87BE42FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882125E5-F9A4-4097-A06B-E433C4276AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2FFDA8E8-6428-4D51-9D6D-F314F8731DBF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>ID</t>
   </si>
@@ -291,6 +291,27 @@
   </si>
   <si>
     <t>El usuario con perfil de estudiante deberá poder acceder a las diferentes redes de apoyo disponibles en caso de necesitarlas.</t>
+  </si>
+  <si>
+    <t>CP-5</t>
+  </si>
+  <si>
+    <t>CP-5.1</t>
+  </si>
+  <si>
+    <t>CP-5.2</t>
+  </si>
+  <si>
+    <t>CP-5.3</t>
+  </si>
+  <si>
+    <t>CP-5.4</t>
+  </si>
+  <si>
+    <t>CP-5.5</t>
+  </si>
+  <si>
+    <t>CP-5.6</t>
   </si>
 </sst>
 </file>
@@ -456,31 +477,31 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -838,135 +859,135 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="2:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <v>45848</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="2:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="13"/>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
@@ -993,23 +1014,23 @@
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="10"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -1028,16 +1049,16 @@
       <c r="H12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="18"/>
     </row>
     <row r="13" spans="2:11" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
@@ -1056,12 +1077,12 @@
       <c r="H13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="12"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B14" s="10"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="9" t="s">
         <v>19</v>
       </c>
@@ -1080,12 +1101,12 @@
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="12"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="10"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="9" t="s">
         <v>44</v>
       </c>
@@ -1104,12 +1125,12 @@
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="12"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="18"/>
     </row>
     <row r="16" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B16" s="10"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="9" t="s">
         <v>45</v>
       </c>
@@ -1128,12 +1149,12 @@
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="12"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B17" s="10"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="9" t="s">
         <v>46</v>
       </c>
@@ -1152,28 +1173,28 @@
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="12"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="18"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
     <row r="19" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="10"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="7" t="s">
         <v>25</v>
       </c>
@@ -1192,16 +1213,16 @@
       <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K19" s="12"/>
+      <c r="K19" s="18"/>
     </row>
     <row r="20" spans="2:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="10"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
@@ -1220,12 +1241,12 @@
       <c r="H20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="12"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="18"/>
     </row>
     <row r="21" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B21" s="10"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="7" t="s">
         <v>27</v>
       </c>
@@ -1244,12 +1265,12 @@
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="12"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="18"/>
     </row>
     <row r="22" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="10"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="7" t="s">
         <v>52</v>
       </c>
@@ -1268,12 +1289,12 @@
       <c r="H22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="12"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="23" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B23" s="10"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="7" t="s">
         <v>53</v>
       </c>
@@ -1292,12 +1313,12 @@
       <c r="H23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="12"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="18"/>
     </row>
     <row r="24" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B24" s="10"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="7" t="s">
         <v>54</v>
       </c>
@@ -1316,28 +1337,28 @@
       <c r="H24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="12"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="18"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
     </row>
     <row r="26" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B26" s="10"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="7" t="s">
         <v>61</v>
       </c>
@@ -1356,16 +1377,16 @@
       <c r="H26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K26" s="12"/>
+      <c r="K26" s="18"/>
     </row>
     <row r="27" spans="2:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B27" s="10"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="7" t="s">
         <v>62</v>
       </c>
@@ -1384,12 +1405,12 @@
       <c r="H27" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="12"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="18"/>
     </row>
     <row r="28" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B28" s="10"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="7" t="s">
         <v>63</v>
       </c>
@@ -1408,12 +1429,12 @@
       <c r="H28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="12"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="18"/>
     </row>
     <row r="29" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="10"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="7" t="s">
         <v>64</v>
       </c>
@@ -1432,12 +1453,12 @@
       <c r="H29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="12"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="18"/>
     </row>
     <row r="30" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B30" s="10"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="7" t="s">
         <v>65</v>
       </c>
@@ -1456,12 +1477,12 @@
       <c r="H30" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="12"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="18"/>
     </row>
     <row r="31" spans="2:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B31" s="10"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="7" t="s">
         <v>66</v>
       </c>
@@ -1480,28 +1501,28 @@
       <c r="H31" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="12"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="18"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
     </row>
     <row r="33" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B33" s="10"/>
+      <c r="B33" s="16"/>
       <c r="C33" s="7" t="s">
         <v>72</v>
       </c>
@@ -1520,18 +1541,18 @@
       <c r="H33" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="18" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="34" spans="2:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B34" s="10"/>
+      <c r="B34" s="16"/>
       <c r="C34" s="7" t="s">
         <v>73</v>
       </c>
@@ -1550,12 +1571,12 @@
       <c r="H34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I34" s="12"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="12"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="18"/>
     </row>
     <row r="35" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B35" s="10"/>
+      <c r="B35" s="16"/>
       <c r="C35" s="7" t="s">
         <v>74</v>
       </c>
@@ -1574,12 +1595,12 @@
       <c r="H35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="12"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="12"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="18"/>
     </row>
     <row r="36" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B36" s="10"/>
+      <c r="B36" s="16"/>
       <c r="C36" s="7" t="s">
         <v>75</v>
       </c>
@@ -1598,12 +1619,12 @@
       <c r="H36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="12"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="18"/>
     </row>
     <row r="37" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="10"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="7" t="s">
         <v>76</v>
       </c>
@@ -1622,12 +1643,12 @@
       <c r="H37" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="12"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="12"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="18"/>
     </row>
     <row r="38" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="10"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="7" t="s">
         <v>77</v>
       </c>
@@ -1646,30 +1667,30 @@
       <c r="H38" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I38" s="12"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="12"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="18"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="11" t="s">
+      <c r="B39" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
     </row>
     <row r="40" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B40" s="10"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="7" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>32</v>
@@ -1686,20 +1707,20 @@
       <c r="H40" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="41" spans="2:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B41" s="10"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="7" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>34</v>
@@ -1716,14 +1737,14 @@
       <c r="H41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="12"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="12"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="18"/>
     </row>
     <row r="42" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B42" s="10"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>36</v>
@@ -1740,14 +1761,14 @@
       <c r="H42" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="12"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="18"/>
     </row>
     <row r="43" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B43" s="10"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="7" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>38</v>
@@ -1764,14 +1785,14 @@
       <c r="H43" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="12"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="12"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="18"/>
     </row>
     <row r="44" spans="2:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B44" s="10"/>
+      <c r="B44" s="16"/>
       <c r="C44" s="7" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>80</v>
@@ -1788,14 +1809,14 @@
       <c r="H44" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="12"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="12"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="18"/>
     </row>
     <row r="45" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B45" s="10"/>
+      <c r="B45" s="16"/>
       <c r="C45" s="7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>81</v>
@@ -1812,46 +1833,46 @@
       <c r="H45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="12"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B39:B45"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="I40:I45"/>
+    <mergeCell ref="J40:J45"/>
+    <mergeCell ref="K40:K45"/>
+    <mergeCell ref="B32:B38"/>
+    <mergeCell ref="C32:K32"/>
+    <mergeCell ref="I33:I38"/>
+    <mergeCell ref="J33:J38"/>
+    <mergeCell ref="K33:K38"/>
+    <mergeCell ref="B25:B31"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="I26:I31"/>
+    <mergeCell ref="J26:J31"/>
+    <mergeCell ref="K26:K31"/>
+    <mergeCell ref="B18:B24"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="I19:I24"/>
+    <mergeCell ref="J19:J24"/>
+    <mergeCell ref="K19:K24"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
     <mergeCell ref="C7:K7"/>
     <mergeCell ref="C8:K8"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="C9:K9"/>
     <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
     <mergeCell ref="B11:B17"/>
     <mergeCell ref="J12:J17"/>
     <mergeCell ref="I12:I17"/>
     <mergeCell ref="K12:K17"/>
-    <mergeCell ref="B18:B24"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="I19:I24"/>
-    <mergeCell ref="J19:J24"/>
-    <mergeCell ref="K19:K24"/>
-    <mergeCell ref="B25:B31"/>
-    <mergeCell ref="C25:K25"/>
-    <mergeCell ref="I26:I31"/>
-    <mergeCell ref="J26:J31"/>
-    <mergeCell ref="K26:K31"/>
-    <mergeCell ref="B32:B38"/>
-    <mergeCell ref="C32:K32"/>
-    <mergeCell ref="I33:I38"/>
-    <mergeCell ref="J33:J38"/>
-    <mergeCell ref="K33:K38"/>
-    <mergeCell ref="B39:B45"/>
-    <mergeCell ref="C39:K39"/>
-    <mergeCell ref="I40:I45"/>
-    <mergeCell ref="J40:J45"/>
-    <mergeCell ref="K40:K45"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
